--- a/Salary and Attendence Register.xlsx
+++ b/Salary and Attendence Register.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="19126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup 23-08-17\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="12_ncr:500000_{D754BCD9-5E37-4953-920F-5B49C2C35C26}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="179016"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="61">
   <si>
     <t>Father's Name</t>
   </si>
@@ -182,12 +181,39 @@
   </si>
   <si>
     <t>BASIC SALARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emp id </t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Absent Days</t>
+  </si>
+  <si>
+    <t>Present Days</t>
+  </si>
+  <si>
+    <t>Per Days Salary</t>
+  </si>
+  <si>
+    <t>Cash in Hand</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="[$-409]d/mmm;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -284,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -372,6 +398,15 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -384,20 +419,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -486,23 +544,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -538,23 +579,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -730,7 +754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AX12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -787,19 +811,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="38" t="s">
         <v>23</v>
       </c>
       <c r="F1" s="8" t="s">
@@ -898,42 +922,42 @@
       <c r="AK1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AL1" s="39" t="s">
+      <c r="AL1" s="35" t="s">
         <v>52</v>
       </c>
       <c r="AM1" s="20"/>
       <c r="AN1" s="20"/>
       <c r="AO1" s="20"/>
       <c r="AP1" s="20"/>
-      <c r="AQ1" s="39" t="s">
+      <c r="AQ1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" s="39" t="s">
+      <c r="AR1" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AS1" s="39" t="s">
+      <c r="AS1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="AT1" s="37" t="s">
+      <c r="AT1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="39" t="s">
+      <c r="AU1" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="AV1" s="37" t="s">
+      <c r="AV1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="39" t="s">
+      <c r="AW1" s="35" t="s">
         <v>47</v>
       </c>
       <c r="AX1" s="27"/>
     </row>
     <row r="2" spans="1:50" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
       <c r="F2" s="8" t="s">
         <v>36</v>
       </c>
@@ -1030,7 +1054,7 @@
       <c r="AK2" s="17">
         <v>31</v>
       </c>
-      <c r="AL2" s="38"/>
+      <c r="AL2" s="34"/>
       <c r="AM2" s="26" t="s">
         <v>41</v>
       </c>
@@ -1043,13 +1067,13 @@
       <c r="AP2" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="38"/>
+      <c r="AQ2" s="34"/>
+      <c r="AR2" s="34"/>
+      <c r="AS2" s="34"/>
+      <c r="AT2" s="34"/>
+      <c r="AU2" s="34"/>
+      <c r="AV2" s="34"/>
+      <c r="AW2" s="34"/>
       <c r="AX2" s="27"/>
     </row>
     <row r="3" spans="1:50" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -2514,6 +2538,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="AV1:AV2"/>
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AQ1:AQ2"/>
@@ -2522,11 +2551,6 @@
     <mergeCell ref="AS1:AS2"/>
     <mergeCell ref="AT1:AT2"/>
     <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2534,7 +2558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2543,10 +2567,603 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A6:AL11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="35" max="35" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="40">
+        <v>45658</v>
+      </c>
+      <c r="E6" s="40">
+        <v>45659</v>
+      </c>
+      <c r="F6" s="40">
+        <v>45660</v>
+      </c>
+      <c r="G6" s="40">
+        <v>45661</v>
+      </c>
+      <c r="H6" s="40">
+        <v>45662</v>
+      </c>
+      <c r="I6" s="40">
+        <v>45663</v>
+      </c>
+      <c r="J6" s="40">
+        <v>45664</v>
+      </c>
+      <c r="K6" s="40">
+        <v>45665</v>
+      </c>
+      <c r="L6" s="40">
+        <v>45666</v>
+      </c>
+      <c r="M6" s="40">
+        <v>45667</v>
+      </c>
+      <c r="N6" s="40">
+        <v>45668</v>
+      </c>
+      <c r="O6" s="40">
+        <v>45669</v>
+      </c>
+      <c r="P6" s="40">
+        <v>45670</v>
+      </c>
+      <c r="Q6" s="40">
+        <v>45671</v>
+      </c>
+      <c r="R6" s="40">
+        <v>45672</v>
+      </c>
+      <c r="S6" s="40">
+        <v>45673</v>
+      </c>
+      <c r="T6" s="40">
+        <v>45674</v>
+      </c>
+      <c r="U6" s="40">
+        <v>45675</v>
+      </c>
+      <c r="V6" s="40">
+        <v>45676</v>
+      </c>
+      <c r="W6" s="40">
+        <v>45677</v>
+      </c>
+      <c r="X6" s="40">
+        <v>45678</v>
+      </c>
+      <c r="Y6" s="40">
+        <v>45679</v>
+      </c>
+      <c r="Z6" s="40">
+        <v>45680</v>
+      </c>
+      <c r="AA6" s="40">
+        <v>45681</v>
+      </c>
+      <c r="AB6" s="40">
+        <v>45682</v>
+      </c>
+      <c r="AC6" s="40">
+        <v>45683</v>
+      </c>
+      <c r="AD6" s="40">
+        <v>45684</v>
+      </c>
+      <c r="AE6" s="40">
+        <v>45685</v>
+      </c>
+      <c r="AF6" s="40">
+        <v>45686</v>
+      </c>
+      <c r="AG6" s="40">
+        <v>45687</v>
+      </c>
+      <c r="AH6" s="40">
+        <v>45688</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>25100</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI7" s="3">
+        <f>COUNTIF(D7:AH7,"A")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ7" s="3">
+        <f>COUNTIF(D7:AH7,"P")</f>
+        <v>29</v>
+      </c>
+      <c r="AK7" s="3">
+        <f>C7/31</f>
+        <v>809.67741935483866</v>
+      </c>
+      <c r="AL7" s="3">
+        <f>AK7*AJ7</f>
+        <v>23480.645161290322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>32510</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI8" s="3">
+        <f t="shared" ref="AI8:AI10" si="0">COUNTIF(D8:AH8,"A")</f>
+        <v>6</v>
+      </c>
+      <c r="AJ8" s="3">
+        <f t="shared" ref="AJ8:AJ9" si="1">COUNTIF(D8:AH8,"P")</f>
+        <v>25</v>
+      </c>
+      <c r="AK8" s="3">
+        <f t="shared" ref="AK8:AK10" si="2">C8/31</f>
+        <v>1048.7096774193549</v>
+      </c>
+      <c r="AL8" s="3">
+        <f t="shared" ref="AL8:AL10" si="3">AK8*AJ8</f>
+        <v>26217.741935483871</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>3621</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI9" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AK9" s="3">
+        <f t="shared" si="2"/>
+        <v>116.80645161290323</v>
+      </c>
+      <c r="AL9" s="3">
+        <f t="shared" si="3"/>
+        <v>3387.3870967741937</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>2541</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3">
+        <f>COUNTIF(D10:AH10,"P")</f>
+        <v>31</v>
+      </c>
+      <c r="AK10" s="3">
+        <f t="shared" si="2"/>
+        <v>81.967741935483872</v>
+      </c>
+      <c r="AL10" s="3">
+        <f t="shared" si="3"/>
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D7:AH10">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="p">
+      <formula>NOT(ISERROR(SEARCH("p",D7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="A">
+      <formula>NOT(ISERROR(SEARCH("A",D7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>